--- a/1kredit-serp-competitors.xlsx
+++ b/1kredit-serp-competitors.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Топ-10 выдачи" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Конкуренты" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="xT по доменам" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Топ-10 выдачи'!$A$1:$G$301</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Конкуренты'!$A$1:$G$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Топ-10 выдачи'!$A$1:$H$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Конкуренты'!$A$1:$H$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'xT по доменам'!$A$1:$C$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G301"/>
+  <dimension ref="A1:H301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -451,8 +453,9 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,10 +486,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>xT</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
@@ -516,10 +524,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>https://auto.bankffin.kz/</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -549,10 +562,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>https://eubank.kz/ru/loan-for-new-car</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -582,10 +600,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/credit/v-salonah-partnerah</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -615,10 +638,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>https://mycarfinance.kz/</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -648,10 +676,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/new_auto</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -681,10 +714,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/autocredits</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -714,10 +752,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/auto-loan</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -747,10 +790,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>https://guide.kaspi.kz/client/ru/auto_credit</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -780,10 +828,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>https://www.vbr.kz/autokredity/calculator/</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -813,10 +866,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/auto-credit-for-new-car/</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -846,10 +904,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>https://avto-dengi.kz/</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -879,10 +942,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>https://lombard-b.kz/cars/</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -912,10 +980,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>https://avto-lombard.kz/</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -945,10 +1018,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>https://2gis.kz/astana/search/Автоломбарды</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Справочник</t>
         </is>
@@ -978,10 +1056,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>https://auto-money.kz/</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1011,10 +1094,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>https://www.instagram.com/auto_money.kz/</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Соцсети</t>
         </is>
@@ -1044,10 +1132,15 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>https://zhana-credit.kz/shymkent/</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -1077,10 +1170,15 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>https://2gis.kz/almaty/search/Автоломбарды</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Справочник</t>
         </is>
@@ -1110,10 +1208,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>https://astana.credit-auto.kz/</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1143,10 +1246,15 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>https://lombard-econom.kz/</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1176,10 +1284,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>https://avto-lombard.kz/</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1209,10 +1322,15 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>https://lombard-b.kz/cars/</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1242,10 +1360,15 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>https://auto-money.kz/</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1275,10 +1398,15 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>https://www.instagram.com/auto_money.kz/</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Соцсети</t>
         </is>
@@ -1308,10 +1436,15 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>https://lombard-econom.kz/</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1341,10 +1474,15 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>https://seiflombard.kz/ru/zaim-pod-zalog-avto/</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1374,10 +1512,15 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>https://2gis.kz/almaty/search/Автоломбард</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Справочник</t>
         </is>
@@ -1407,10 +1550,15 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>https://lombard-almaty.kz/uslugi/s-pravom-vozhdeniya/</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1440,10 +1588,15 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>https://avto-dengi.kz/</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1473,10 +1626,15 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>https://zhana-credit.kz/</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -1506,10 +1664,15 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>https://solva.kz/business/pod-zalog-auto/</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -1539,10 +1702,15 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>https://kmf.kz/kz/news-inner/kredit-pod-zalog-avto-instruktsiya-ot-a-do-ya/</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -1572,10 +1740,15 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>https://tascredit.kz/ru/loans/credit-pod-zalog-s-pravom-vozhdeniya/</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -1605,10 +1778,15 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>https://lombard-b.kz/cars-new/</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1638,10 +1816,15 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>https://avto-dengi.kz/</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1671,10 +1854,15 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>https://2gis.kz/astana/search/Авто кредит под залог</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Справочник</t>
         </is>
@@ -1704,10 +1892,15 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>https://prodengi.kz/kredit-pod-zalog-avto</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -1737,10 +1930,15 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>8.95</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>https://www.gazprombank.ru/personal/avtokredit/6483887/</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -1770,10 +1968,15 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>https://auto-money.kz/bail-money/</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1803,10 +2006,15 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>https://tascredit.kz/ru/kredit-pod-zalog-s-pravom-vozhdeniya-shymkent/</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -1836,10 +2044,15 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>https://solva.kz/business/pod-zalog-auto/</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -1869,10 +2082,15 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>https://kmf.kz/kz/news-inner/kredit-pod-zalog-avto-instruktsiya-ot-a-do-ya/</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -1902,10 +2120,15 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>https://tascredit.kz/ru/loans/credit-pod-zalog-s-pravom-vozhdeniya/</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -1935,10 +2158,15 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>https://avto-dengi.kz/</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -1968,10 +2196,15 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>https://lombard-b.kz/auto-pod-zalog/</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -2001,10 +2234,15 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>https://vsebanki.kz/ru/credits/zalogovyi-kredit/pod-zalog-avto</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -2034,10 +2272,15 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>https://auto-money.kz/bail-money/</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -2067,10 +2310,15 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>http://jetcar.kz/cash/credit</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -2100,10 +2348,15 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>https://prodengi.kz/kredit-pod-zalog-avto</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -2133,10 +2386,15 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>https://cashdrive.kz/</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -2166,10 +2424,15 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/zalog_credit</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2199,10 +2462,15 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/mortgage-loan/</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2232,10 +2500,15 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/index.php/knowledge_base/725</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2265,10 +2538,15 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/credit-real-estate</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2298,10 +2576,15 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>https://kmf.kz/news-inner/mikrokredit-pod-zalog-nedvizhimosti-plyusy-i-riski/</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -2331,10 +2614,15 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/neotlozhnye-nuzhdy</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2364,10 +2652,15 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/nuzhnyy-kredit-pod-zalog-s-podtverzhdeniem-dohoda</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2397,10 +2690,15 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
           <t>https://capitalinvest.kz/</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -2430,10 +2728,15 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>https://2gis.kz/almaty/search/Кредит под залог недвижимости</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Справочник</t>
         </is>
@@ -2463,10 +2766,15 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
           <t>https://www.vbr.kz/banki/kredity/zalog/</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -2496,10 +2804,15 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/zalog_credit</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2529,10 +2842,15 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/mortgage-loan/</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2562,10 +2880,15 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/credit-real-estate</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2595,10 +2918,15 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
           <t>https://www.vbr.kz/banki/kredity/zalog/</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -2628,10 +2956,15 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
           <t>https://kmf.kz/news-inner/mikrokredit-pod-zalog-nedvizhimosti-plyusy-i-riski/</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -2661,10 +2994,15 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/neotlozhnye-nuzhdy</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2694,10 +3032,15 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
           <t>https://prodengi.kz/astana/credits/home-equity-loan</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -2727,10 +3070,15 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
           <t>https://vsebanki.kz/ru/credits/zalogovyi-kredit/kredit-pod-zalog-imushhestva</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -2760,10 +3108,15 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/business/credit/digital-loan</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2793,10 +3146,15 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/nuzhnyy-kredit-pod-zalog-s-podtverzhdeniem-dohoda</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2826,10 +3184,15 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/zalog_credit</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2859,10 +3222,15 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/index.php/knowledge_base/725</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2892,10 +3260,15 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
           <t>https://kmf.kz/news-inner/mikrokredit-pod-zalog-nedvizhimosti-plyusy-i-riski/</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -2925,10 +3298,15 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/mortgage-loan/</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2958,10 +3336,15 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/credit-real-estate</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -2991,10 +3374,15 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/neotlozhnye-nuzhdy</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3024,10 +3412,15 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/nuzhnyy-kredit-pod-zalog-s-podtverzhdeniem-dohoda</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3057,10 +3450,15 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>https://tascredit.kz/ru/loans/tasmicrofinance/</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -3090,10 +3488,15 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
           <t>https://capitalinvest.kz/</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -3123,10 +3526,15 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
           <t>https://lombard-almaty.kz/uslugi/kredit-pod-zalog-nedvizhimosti/</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Ломбард</t>
         </is>
@@ -3156,10 +3564,15 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/ipoteka</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3189,10 +3602,15 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/mortgage-loan/</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3222,10 +3640,15 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
           <t>https://www.vbr.kz/banki/ipoteka/zalog/</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -3255,10 +3678,15 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/credit-real-estate</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3288,10 +3716,15 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
           <t>https://bankffin.kz/ipoteka/</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3321,10 +3754,15 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
+          <t>4.59</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
           <t>https://hcsbk.kz/ru/onlain-ipoteka/</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3354,10 +3792,15 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/zalog_credit</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3387,10 +3830,15 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>https://kzibank.kz/ru/home-loan--real-estate</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3420,10 +3868,15 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
+          <t>5.39</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
           <t>https://krisha.kz/kz/content/articles/2024/</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>Портал</t>
         </is>
@@ -3453,10 +3906,15 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
           <t>https://prodengi.kz/credits/home-equity-loan</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -3486,10 +3944,15 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/zalog_credit</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3519,10 +3982,15 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/mortgage-loan/</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3552,10 +4020,15 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/index.php/knowledge_base/725</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3585,10 +4058,15 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/credit-real-estate</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3618,10 +4096,15 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
           <t>https://kmf.kz/news-inner/mikrokredit-pod-zalog-nedvizhimosti-plyusy-i-riski/</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -3651,10 +4134,15 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/neotlozhnye-nuzhdy</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3684,10 +4172,15 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/nuzhnyy-kredit-pod-zalog-s-podtverzhdeniem-dohoda</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3717,10 +4210,15 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
           <t>https://2gis.kz/almaty/search/Кредит под залог недвижимости</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Справочник</t>
         </is>
@@ -3750,10 +4248,15 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/zalog_any</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3783,10 +4286,15 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
           <t>https://prodengi.kz/astana/credits/home-equity-loan</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -3816,10 +4324,15 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/business/loans/ip-online-credit/</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3849,10 +4362,15 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
           <t>https://kmf.kz/business/kmf-biznes/</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -3882,10 +4400,15 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/business/credit/onlainkredit-ip</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3915,10 +4438,15 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
           <t>https://alataucitybank.kz/business/credits/online</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3948,10 +4476,15 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/small_business/credits/business</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -3981,10 +4514,15 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
           <t>https://solva.kz/business/</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -4014,10 +4552,15 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
           <t>https://www.vtb-bank.kz/smallbusiness/kredity/kreditovanie-malogo-biznesa/kredit-moment-ip/</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4047,10 +4590,15 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
           <t>https://guide.kaspi.kz/client/ru/credit_entrepreneurs/conditions/q14678</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4080,10 +4628,15 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/business/government-programm-damu/</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4113,10 +4666,15 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
           <t>https://business.bankffin.kz/</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4146,10 +4704,15 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/business/loans/ip-online-credit/</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4179,10 +4742,15 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
           <t>https://alataucitybank.kz/business/credits/online</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4212,10 +4780,15 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
           <t>https://kmf.kz/business/kmf-biznes/</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -4245,10 +4818,15 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/small_business/credits/business</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4278,10 +4856,15 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/business/credit/onlainkredit-ip</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4311,10 +4894,15 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
           <t>https://www.vtb-bank.kz/smallbusiness/kredity/kreditovanie-malogo-biznesa/kredit-moment-ip/</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4344,10 +4932,15 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
           <t>https://solva.kz/business/</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -4377,10 +4970,15 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
           <t>https://guide.kaspi.kz/client/ru/credit_entrepreneurs/conditions/q14678</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4410,10 +5008,15 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/business/government-programm-damu/</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4443,10 +5046,15 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
           <t>https://www.vbr.kz/banki/kredity-dlya-biznesa/</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -4476,10 +5084,15 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/business/loans/ip-online-credit/</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4509,10 +5122,15 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
           <t>https://business.bankffin.kz/</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4542,10 +5160,15 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/business/credit/onlainkredit-ip</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4575,10 +5198,15 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
           <t>https://kmf.kz/business/kmf-biznes/</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -4608,10 +5236,15 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
           <t>https://alataucitybank.kz/business/credits/online</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4641,10 +5274,15 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
           <t>https://solva.kz/business/</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -4674,10 +5312,15 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/small_business/credits/business</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4707,10 +5350,15 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
           <t>https://guide.kaspi.kz/client/ru/credit_entrepreneurs</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4740,10 +5388,15 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
           <t>https://www.vtb-bank.kz/smallbusiness/kredity/kreditovanie-malogo-biznesa/kredit-moment-ip/</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4773,10 +5426,15 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/business/government-programm-damu/</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4806,10 +5464,15 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/business/loans/ip-online-credit/</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4839,10 +5502,15 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
           <t>https://business.bankffin.kz/</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4872,10 +5540,15 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
           <t>https://kmf.kz/business/kmf-biznes/</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -4905,10 +5578,15 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/business/credit/onlainkredit-ip</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4938,10 +5616,15 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/small_business/credits/business</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="H136" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -4971,10 +5654,15 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/business/government-programm-damu/</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5004,10 +5692,15 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
           <t>https://www.vtb-bank.kz/smallbusiness/kredity/kreditovanie-malogo-biznesa/kredit-moment-ip/</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5037,10 +5730,15 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
           <t>https://solva.kz/business/</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -5070,10 +5768,15 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/msb/loans</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5103,10 +5806,15 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
           <t>https://business.forte.kz/ru/credits</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="H141" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5136,10 +5844,15 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/business/loans/ip-online-credit/</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="H142" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5169,10 +5882,15 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
           <t>https://kmf.kz/business/kmf-biznes/</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -5202,10 +5920,15 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/small_business/credits/business</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="H144" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5235,10 +5958,15 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
           <t>https://www.vbr.kz/banki/kredity-dlya-biznesa/</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="H145" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -5268,10 +5996,15 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
           <t>https://alataucitybank.kz/business/credits/online</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5301,10 +6034,15 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/business/credit/halyk-predprinimatel</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5334,10 +6072,15 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/business/government-programm-damu/</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5367,10 +6110,15 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
           <t>https://nurbank.kz/ru/legal/credits/support-domestic-trade-entities/</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="H149" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5400,10 +6148,15 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
           <t>https://www.vtb-bank.kz/smallbusiness/kredity/kreditovanie-malogo-biznesa/kredit-moment-ip/</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5433,10 +6186,15 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
           <t>https://solva.kz/business/</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="H151" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -5466,10 +6224,15 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/refinansirovanie</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="H152" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5499,10 +6262,15 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/credit/refinans</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="H153" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5532,10 +6300,15 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/refinansirovanie</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5565,10 +6338,15 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/refinancing</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="H155" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5598,10 +6376,15 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
           <t>https://nurbank.kz/ru/person/credits/external-refinancing/</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="H156" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5631,10 +6414,15 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/refenansirovanie</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="H157" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5664,10 +6452,15 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
           <t>https://kmf.kz/kz/news-inner/refinansirovanie-kredita-kak-gramotno-ispolzovat/</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="H158" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -5697,10 +6490,15 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/refinancing/</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="H159" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5730,10 +6528,15 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
           <t>https://www.vbr.kz/banki/kredity/refinansirovanie/</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="H160" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -5763,10 +6566,15 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
           <t>https://eubank.kz/ru/external-refinancing</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5796,10 +6604,15 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/refinansirovanie</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="H162" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5829,10 +6642,15 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/credit/refinans</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="H163" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5862,10 +6680,15 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/refinancing</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="H164" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5895,10 +6718,15 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
           <t>https://eubank.kz/ru/external-refinancing</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="H165" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5928,10 +6756,15 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/refenansirovanie</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
+      <c r="H166" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5961,10 +6794,15 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
           <t>https://nurbank.kz/ru/person/credits/external-refinancing/</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="H167" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -5994,10 +6832,15 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
           <t>https://www.vbr.kz/banki/kredity/refinansirovanie/</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
+      <c r="H168" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -6027,10 +6870,15 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/refinansirovanie</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="H169" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6060,10 +6908,15 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
           <t>https://kmf.kz/news-inner/refinansirovanie-kredita-kak-gramotno-ispolzovat/</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="H170" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -6093,10 +6946,15 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
+          <t>8.84</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
           <t>https://www.raiffeisen.ru/wiki/chto-takoe-refinansirovanie-kredita/</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="H171" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -6126,10 +6984,15 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/refinansirovanie</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="H172" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6159,10 +7022,15 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/refenansirovanie</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="H173" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6192,10 +7060,15 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/refinancing</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="H174" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6225,10 +7098,15 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
           <t>https://nurbank.kz/ru/person/credits/external-refinancing/</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="H175" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6258,10 +7136,15 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/credit/refinans</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
+      <c r="H176" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6291,10 +7174,15 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
           <t>https://eubank.kz/ru/external-refinancing</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
+      <c r="H177" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6324,10 +7212,15 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/refinansirovanie</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="H178" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6357,10 +7250,15 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
           <t>https://kmf.kz/kz/news-inner/refinansirovanie-kredita-kak-gramotno-ispolzovat/</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="H179" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -6390,10 +7288,15 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
           <t>https://ru.wikipedia.org/wiki/Рефинансирование</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="H180" t="inlineStr">
         <is>
           <t>Инфо</t>
         </is>
@@ -6423,10 +7326,15 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
           <t>https://ru.wikipedia.org/wiki/Рефинансирование</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
+      <c r="H181" t="inlineStr">
         <is>
           <t>Инфо</t>
         </is>
@@ -6456,10 +7364,15 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/refinancing/</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="H182" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6489,10 +7402,15 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
+          <t>6.34</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
           <t>https://www.banki.ru/products/credits/catalogue/refinansirovanie_kredita/</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
+      <c r="H183" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -6522,10 +7440,15 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
+          <t>8.86</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
           <t>https://www.sberbank.ru/ru/person/credits/money/consumer_refinance</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="H184" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -6555,10 +7478,15 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/credit/refinans</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="H185" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6588,10 +7516,15 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/refinansirovanie</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
+      <c r="H186" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6621,10 +7554,15 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/refenansirovanie</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
+      <c r="H187" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6654,10 +7592,15 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
+          <t>8.84</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
           <t>https://www.raiffeisen.ru/wiki/chto-takoe-refinansirovanie-kredita/</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
+      <c r="H188" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -6687,10 +7630,15 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
+          <t>7.59</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
           <t>https://uralsib.ru/kredity/refinansirovanie</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
+      <c r="H189" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -6720,10 +7668,15 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
           <t>https://kmf.kz/kz/news-inner/refinansirovanie-kredita-kak-gramotno-ispolzovat/</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
+      <c r="H190" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -6753,10 +7706,15 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
+          <t>4.59</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
           <t>https://hcsbk.kz/ru/to-get-a-loan/helpful-information/mortgage-refinancing/</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
+      <c r="H191" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6786,10 +7744,15 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/refinancing</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
+      <c r="H192" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6819,10 +7782,15 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
           <t>https://sovcombank.ru/apply/credit/refinansirovanie-kredita/bez-otkaza/</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
+      <c r="H193" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -6852,10 +7820,15 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/refinansirovanie</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
+      <c r="H194" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6885,10 +7858,15 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
           <t>https://www.vbr.kz/banki/kredity/refinansirovanie/</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
+      <c r="H195" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -6918,10 +7896,15 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
           <t>https://alataucitybank.kz/business/credits/refinancing</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
+      <c r="H196" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6951,10 +7934,15 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
           <t>https://nurbank.kz/ru/person/credits/external-refinancing/</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="H197" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -6984,10 +7972,15 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
           <t>https://kmf.kz/kz/news-inner/refinansirovanie-kredita-kak-gramotno-ispolzovat/</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
+      <c r="H198" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -7017,10 +8010,15 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/refinancing/</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
+      <c r="H199" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -7050,10 +8048,15 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/refinansirovanie</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
+      <c r="H200" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -7083,10 +8086,15 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/refenansirovanie</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
+      <c r="H201" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -7116,10 +8124,15 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
+          <t>8.86</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
           <t>https://www.sberbank.ru/ru/person/credits/collection/debt_restructuring</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="H202" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -7149,10 +8162,15 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
           <t>https://home.kz/blog/restrukturizatsiya-kredita-chto-eto-takoe</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="H203" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -7182,10 +8200,15 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
           <t>https://kmf.kz/news-inner/restrukturizatsiya-kredita-chto-eto-takoe-kak-vospolzovatsya-v-kazakhstane/</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="H204" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -7215,10 +8238,15 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
           <t>https://www.gov.kz/memleket/entities/ardfm/press/news/details/457127?lang=ru</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
+      <c r="H205" t="inlineStr">
         <is>
           <t>Гос</t>
         </is>
@@ -7248,10 +8276,15 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
+          <t>8.95</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
           <t>https://www.gazprombank.ru/pro-finance/credit/restrukturizatsiya-kredita/</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
+      <c r="H206" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -7281,10 +8314,15 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
+          <t>9.12</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
           <t>https://www.vtb.ru/malyj-biznes/biznes-slovar/kredity/restrukturizaciya/</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="H207" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -7314,10 +8352,15 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
           <t>https://pay.yandex.ru/blog/articles/restrukturizaciya-kredita-chto-eto-takoe</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="H208" t="inlineStr">
         <is>
           <t>Инфо</t>
         </is>
@@ -7347,10 +8390,15 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
           <t>https://xn----dtbeec7ak4ay9j.xn--p1ai/blog/restrukturizatsiya-kredita/</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="H209" t="inlineStr">
         <is>
           <t>Инфо</t>
         </is>
@@ -7380,10 +8428,15 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
+          <t>8.84</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
           <t>https://www.raiffeisen.ru/wiki/refinansirovanie-i-restrukturizatsiya/</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="H210" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -7413,10 +8466,15 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
           <t>https://www.youtube.com/watch?v=8Tf6rA9_sSY</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="H211" t="inlineStr">
         <is>
           <t>Соцсети</t>
         </is>
@@ -7446,10 +8504,15 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
+          <t>8.86</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
           <t>https://www.sberbank.ru/ru/person/credits/collection/debt_restructuring</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
+      <c r="H212" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -7479,10 +8542,15 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
           <t>https://home.kz/blog/restrukturizatsiya-kredita-chto-eto-takoe</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
+      <c r="H213" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -7512,10 +8580,15 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
           <t>https://www.gov.kz/memleket/entities/ardfm/press/news/details/457127?lang=ru</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
+      <c r="H214" t="inlineStr">
         <is>
           <t>Гос</t>
         </is>
@@ -7545,10 +8618,15 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
           <t>https://ru.wikipedia.org/wiki/Реструктуризация_государственного_долга</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
+      <c r="H215" t="inlineStr">
         <is>
           <t>Инфо</t>
         </is>
@@ -7578,10 +8656,15 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
           <t>https://alfabank.ru/help/articles/credit/refinansirovanie-i-restrukturizatsiya/</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
+      <c r="H216" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -7611,10 +8694,15 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
+          <t>9.12</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
           <t>https://www.vtb.ru/malyj-biznes/biznes-slovar/kredity/restrukturizaciya/</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="H217" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -7644,10 +8732,15 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
+          <t>7.82</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
           <t>https://www.mtsbank.ru/articles/restrukturizatsiya-kredita-chto-eto/</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
+      <c r="H218" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -7677,10 +8770,15 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
+          <t>5.97</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
           <t>https://maritimebank.com/blog/rko/chto-takoe-restrukturizatsiya-kredita/</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="H219" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -7710,10 +8808,15 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
+          <t>8.95</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
           <t>https://www.gazprombank.ru/pro-finance/credit/restrukturizatsiya-kredita/</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="H220" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -7743,10 +8846,15 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
           <t>https://www.instagram.com/reel/DP5-FlajVWR/</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="H221" t="inlineStr">
         <is>
           <t>Соцсети</t>
         </is>
@@ -7776,10 +8884,15 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
           <t>https://www.gov.kz/memleket/entities/ardfm/press/news/details/457127?lang=ru</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="H222" t="inlineStr">
         <is>
           <t>Гос</t>
         </is>
@@ -7809,10 +8922,15 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
+          <t>8.86</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
           <t>https://www.sberbank.ru/ru/person/credits/collection/debt_restructuring</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="H223" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -7842,10 +8960,15 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
           <t>https://cdb.kz/sistema/novosti/o_protsedure_restrukturizatsii_zadolzhennosti/</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
+      <c r="H224" t="inlineStr">
         <is>
           <t>Гос</t>
         </is>
@@ -7875,10 +8998,15 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
           <t>https://ru.wikipedia.org/wiki/Реструктуризация_государственного_долга</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
+      <c r="H225" t="inlineStr">
         <is>
           <t>Инфо</t>
         </is>
@@ -7908,10 +9036,15 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
           <t>https://kmf.kz/news-inner/restrukturizatsiya-kredita-chto-eto-takoe-kak-vospolzovatsya-v-kazakhstane/</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
+      <c r="H226" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -7941,10 +9074,15 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
+          <t>8.84</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
           <t>https://www.raiffeisen.ru/wiki/refinansirovanie-i-restrukturizatsiya/</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="H227" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -7974,10 +9112,15 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
+          <t>7.82</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
           <t>https://www.mtsbank.ru/articles/restrukturizatsiya-kredita-chto-eto/</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="H228" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -8007,10 +9150,15 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
+          <t>5.81</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
           <t>https://domrfbank.ru/blog/refinansirovanie-i-restrukturizatsiya/</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
+      <c r="H229" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -8040,10 +9188,15 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
           <t>https://www.instagram.com/reel/DQBQENkjIi6/</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
+      <c r="H230" t="inlineStr">
         <is>
           <t>Соцсети</t>
         </is>
@@ -8073,10 +9226,15 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
+          <t>6.34</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
           <t>https://www.banki.ru/products/credits/catalogue/restruktucrizaciya-kredita/</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
+      <c r="H231" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -8106,10 +9264,15 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
           <t>https://home.kz/blog/restrukturizatsiya-kredita-chto-eto-takoe</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="H232" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -8139,10 +9302,15 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
+          <t>8.86</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
           <t>https://www.sberbank.ru/ru/person/credits/collection/debt_restructuring</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
+      <c r="H233" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -8172,10 +9340,15 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
+          <t>7.82</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
           <t>https://www.mtsbank.ru/articles/restrukturizatsiya-kredita-chto-eto/</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="H234" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -8205,10 +9378,15 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
           <t>https://www.gov.kz/memleket/entities/ardfm/press/news/details/457127?lang=ru</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="H235" t="inlineStr">
         <is>
           <t>Гос</t>
         </is>
@@ -8238,10 +9416,15 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
           <t>https://alfabank.ru/help/articles/credit/refinansirovanie-i-restrukturizatsiya/</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
+      <c r="H236" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -8271,10 +9454,15 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
+          <t>8.95</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
           <t>https://www.gazprombank.ru/pro-finance/credit/restrukturizatsiya-kredita/</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
+      <c r="H237" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -8304,10 +9492,15 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
           <t>https://netdolgoff.ru/blog/kreditnye-problemy/chto-takoe-restrukturizacziya-dolga/</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
+      <c r="H238" t="inlineStr">
         <is>
           <t>Инфо</t>
         </is>
@@ -8337,10 +9530,15 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
+          <t>8.84</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
           <t>https://www.raiffeisen.ru/wiki/refinansirovanie-i-restrukturizatsiya/</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
+      <c r="H239" t="inlineStr">
         <is>
           <t>Банк (RU)</t>
         </is>
@@ -8370,10 +9568,15 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
           <t>https://fpa.ru/info/kak-sdelat-restrukturizaciju-mikrozajma/</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
+      <c r="H240" t="inlineStr">
         <is>
           <t>Инфо</t>
         </is>
@@ -8403,10 +9606,15 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
+          <t>9.62</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
           <t>https://www.consultant.ru/document/cons_doc_LAW_218535/</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
+      <c r="H241" t="inlineStr">
         <is>
           <t>Инфо</t>
         </is>
@@ -8436,10 +9644,15 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/credit/uregulirovanie-problemnoj-zadolzhennosti</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
+      <c r="H242" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -8469,10 +9682,15 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
           <t>https://www.threads.com/@kaspi.kz/post/DUnAR0wCGFQ</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
+      <c r="H243" t="inlineStr">
         <is>
           <t>Соцсети</t>
         </is>
@@ -8502,10 +9720,15 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
           <t>https://kmf.kz/news-inner/restrukturizatsiya-kredita-chto-eto-takoe-kak-vospolzovatsya-v-kazakhstane/</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
+      <c r="H244" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -8535,10 +9758,15 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
           <t>https://www.gov.kz/memleket/entities/ardfm/press/news/details/503614?lang=ru</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
+      <c r="H245" t="inlineStr">
         <is>
           <t>Гос</t>
         </is>
@@ -8568,10 +9796,15 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
           <t>https://guide.kaspi.kz/client/ru/cash_credit/debt/monthly_payment/q268</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
+      <c r="H246" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -8601,10 +9834,15 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
           <t>https://2gis.kz/astana/search/Оптимизация кредита</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
+      <c r="H247" t="inlineStr">
         <is>
           <t>Справочник</t>
         </is>
@@ -8634,10 +9872,15 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
           <t>https://1cbkz.userecho.ru/communities/1/topics/17</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
+      <c r="H248" t="inlineStr">
         <is>
           <t>Инфо</t>
         </is>
@@ -8667,10 +9910,15 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
           <t>https://home.kz/blog/kak-snizit-stavku-po-deystvuyuschemu-kreditu</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
+      <c r="H249" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -8700,10 +9948,15 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
           <t>https://kmf.kz/kz/news-inner/restrukturizatsiya-kredita-chto-eto-takoe/</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
+      <c r="H250" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -8733,10 +9986,15 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
+          <t>4.97</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
           <t>https://sky.pro/wiki/money/chto-takoe-optimizaciya-kredita/</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="H251" t="inlineStr">
         <is>
           <t>Инфо</t>
         </is>
@@ -8766,10 +10024,15 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/neotlozhnye-nuzhdy</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
+      <c r="H252" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -8799,10 +10062,15 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/business/credit/digital-loan</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
+      <c r="H253" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -8832,10 +10100,15 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/credit-real-estate</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
+      <c r="H254" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -8865,10 +10138,15 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/zalog_credit</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
+      <c r="H255" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -8898,10 +10176,15 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/mortgage-loan/</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
+      <c r="H256" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -8931,10 +10214,15 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/nuzhnyy-kredit-pod-zalog-s-podtverzhdeniem-dohoda</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
+      <c r="H257" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -8964,10 +10252,15 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
           <t>https://kmf.kz/news-inner/mikrokredit-pod-zalog-nedvizhimosti-plyusy-i-riski/</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
+      <c r="H258" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -8997,10 +10290,15 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
           <t>https://nurbank.kz/ru/person/credits/collateral-loan/</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
+      <c r="H259" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9030,10 +10328,15 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
           <t>https://kmf.kz/kz/news-inner/chto-takoe-zalogovyj-kredit-i-ego-vidy/</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
+      <c r="H260" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -9063,10 +10366,15 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
           <t>https://solva.kz/business/pod-zalog-auto/</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
+      <c r="H261" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -9096,10 +10404,15 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/mortgage-loan/</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
+      <c r="H262" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9129,10 +10442,15 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/zalog_credit</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
+      <c r="H263" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9162,10 +10480,15 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/credit-real-estate</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
+      <c r="H264" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9195,10 +10518,15 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/neotlozhnye-nuzhdy</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
+      <c r="H265" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9228,10 +10556,15 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/nuzhnyy-kredit-pod-zalog-s-podtverzhdeniem-dohoda</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
+      <c r="H266" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9261,10 +10594,15 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/business/credit/digital-loan</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
+      <c r="H267" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9294,10 +10632,15 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
           <t>https://kmf.kz/news-inner/mikrokredit-pod-zalog-nedvizhimosti-plyusy-i-riski/</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
+      <c r="H268" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -9327,10 +10670,15 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
           <t>https://www.vbr.kz/banki/kredity/zalog/</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
+      <c r="H269" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -9360,10 +10708,15 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
           <t>https://prodengi.kz/astana/credits/home-equity-loan</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
+      <c r="H270" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -9393,10 +10746,15 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
           <t>https://2gis.kz/almaty/search/Кредит под залог недвижимости</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
+      <c r="H271" t="inlineStr">
         <is>
           <t>Справочник</t>
         </is>
@@ -9426,10 +10784,15 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/mortgage-loan/</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
+      <c r="H272" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9459,10 +10822,15 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/zalog_credit</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
+      <c r="H273" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9492,10 +10860,15 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/credit-real-estate</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
+      <c r="H274" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9525,10 +10898,15 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/neotlozhnye-nuzhdy</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
+      <c r="H275" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9558,10 +10936,15 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/business/credit/digital-loan</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
+      <c r="H276" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9591,10 +10974,15 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
           <t>https://kmf.kz/kz/news-inner/chto-takoe-zalogovyj-kredit-i-ego-vidy/</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr">
+      <c r="H277" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -9624,10 +11012,15 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/nuzhnyy-kredit-pod-zalog-s-podtverzhdeniem-dohoda</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr">
+      <c r="H278" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9657,10 +11050,15 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
           <t>https://nurbank.kz/ru/person/credits/collateral-loan/</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
+      <c r="H279" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9690,10 +11088,15 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
           <t>https://finance.kz/articles/kredit-pod-zalog-v-kazakhstane</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
+      <c r="H280" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -9723,10 +11126,15 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/en/faq/82</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr">
+      <c r="H281" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9756,10 +11164,15 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/index.php/knowledge_base/725</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
+      <c r="H282" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9789,10 +11202,15 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/zalog_credit</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr">
+      <c r="H283" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9822,10 +11240,15 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/credit-real-estate</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr">
+      <c r="H284" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9855,10 +11278,15 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/personal/loans/mortgage-loan/</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr">
+      <c r="H285" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9888,10 +11316,15 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/neotlozhnye-nuzhdy</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr">
+      <c r="H286" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9921,10 +11354,15 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
           <t>https://kmf.kz/news-inner/mikrokredit-pod-zalog-nedvizhimosti-plyusy-i-riski/</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
+      <c r="H287" t="inlineStr">
         <is>
           <t>МФО</t>
         </is>
@@ -9954,10 +11392,15 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/nuzhnyy-kredit-pod-zalog-s-podtverzhdeniem-dohoda</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr">
+      <c r="H288" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -9987,10 +11430,15 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
           <t>https://nurbank.kz/ru/person/credits/collateral-loan/</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr">
+      <c r="H289" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -10020,10 +11468,15 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/business/credit/biznes-depozit</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr">
+      <c r="H290" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -10053,10 +11506,15 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
           <t>https://prodengi.kz/astana/credits/home-equity-loan</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr">
+      <c r="H291" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
@@ -10086,10 +11544,15 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
           <t>https://halykbank.kz/business/credit/kreditnyj-kalkulyator-yul</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr">
+      <c r="H292" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -10119,10 +11582,15 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
           <t>https://bank.forte.kz/ru/neotlozhnye-nuzhdy</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr">
+      <c r="H293" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -10152,10 +11620,15 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
           <t>https://www.bcc.kz/bcc-journal/loan-calculator/</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr">
+      <c r="H294" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -10185,10 +11658,15 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/zalog_credit</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr">
+      <c r="H295" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -10218,10 +11696,15 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
           <t>https://altynbank.kz/ru/personal/credit-real-estate</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr">
+      <c r="H296" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -10251,10 +11734,15 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
           <t>https://bankrbk.kz/ru/individuals/loans/nuzhnyy-kredit-pod-zalog-s-podtverzhdeniem-dohoda</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr">
+      <c r="H297" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -10284,10 +11772,15 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
           <t>https://www.vtb-bank.kz/individuals/kreditovanie/kreditnyy-kalkulyator/</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr">
+      <c r="H298" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -10317,10 +11810,15 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
           <t>https://berekebank.kz/ru/personal/credits/zalog_room</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr">
+      <c r="H299" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -10350,10 +11848,15 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
           <t>https://home.kz/loans/kreditnyj-kalkulyator</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr">
+      <c r="H300" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
@@ -10383,17 +11886,22 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
           <t>https://prodengi.kz/credits/home-equity-loan</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr">
+      <c r="H301" t="inlineStr">
         <is>
           <t>Агрегатор</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G301"/>
+  <autoFilter ref="A1:H301"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10404,16 +11912,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10444,12 +11953,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>xT</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Тип компании</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Инфо-выдача кластера %</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Инфо-выдача %</t>
         </is>
       </c>
     </row>
@@ -10477,10 +11991,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Ломбард</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10508,10 +12027,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Ломбард</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10539,10 +12063,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Ломбард</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10570,10 +12099,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Справочник</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10601,10 +12135,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>МФО</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10632,10 +12171,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>МФО</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10663,10 +12207,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>Ломбард</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10694,10 +12243,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>МФО</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10725,10 +12279,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>Соцсети</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10756,10 +12315,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Ломбард</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10787,10 +12351,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Агрегатор</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10818,10 +12387,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>МФО</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10849,10 +12423,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>6</v>
       </c>
     </row>
@@ -10880,10 +12459,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -10911,10 +12495,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
         <v>6</v>
       </c>
     </row>
@@ -10942,10 +12531,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -10973,10 +12567,15 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11004,10 +12603,15 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>МФО</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11035,10 +12639,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11066,10 +12675,15 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Агрегатор</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11097,10 +12711,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>Агрегатор</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11128,10 +12747,15 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>МФО</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11159,10 +12783,15 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>Справочник</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11190,10 +12819,15 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11221,10 +12855,15 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>МФО</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11252,10 +12891,15 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11283,10 +12927,15 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11314,10 +12963,15 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>МФО</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11345,10 +12999,15 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11376,10 +13035,15 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11407,10 +13071,15 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11438,10 +13107,15 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11469,10 +13143,15 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>Агрегатор</t>
         </is>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11500,10 +13179,15 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11531,10 +13215,15 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11562,10 +13251,15 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>МФО</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11593,10 +13287,15 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11624,10 +13323,15 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11655,10 +13359,15 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11686,10 +13395,15 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11717,10 +13431,15 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11748,10 +13467,15 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>Агрегатор</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11779,10 +13503,15 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11810,10 +13539,15 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>8.84</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>Банк (RU)</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11841,10 +13575,15 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>Инфо</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11872,10 +13611,15 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>Гос</t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>40</v>
       </c>
     </row>
@@ -11903,10 +13647,15 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>8.86</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>Банк (RU)</t>
         </is>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>40</v>
       </c>
     </row>
@@ -11934,10 +13683,15 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
         <v>40</v>
       </c>
     </row>
@@ -11965,10 +13719,15 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>МФО</t>
         </is>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>40</v>
       </c>
     </row>
@@ -11996,10 +13755,15 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>7.82</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>Банк (RU)</t>
         </is>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>40</v>
       </c>
     </row>
@@ -12027,10 +13791,15 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>8.95</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>Банк (RU)</t>
         </is>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>40</v>
       </c>
     </row>
@@ -12058,10 +13827,15 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>8.84</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>Банк (RU)</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>40</v>
       </c>
     </row>
@@ -12089,10 +13863,15 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>Инфо</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>40</v>
       </c>
     </row>
@@ -12120,10 +13899,15 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>Банк (RU)</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>40</v>
       </c>
     </row>
@@ -12151,10 +13935,15 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>9.12</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>Банк (RU)</t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>40</v>
       </c>
     </row>
@@ -12182,10 +13971,15 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>Соцсети</t>
         </is>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>40</v>
       </c>
     </row>
@@ -12213,10 +14007,15 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12244,10 +14043,15 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12275,10 +14079,15 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12306,10 +14115,15 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12337,10 +14151,15 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12368,10 +14187,15 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12399,10 +14223,15 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
           <t>МФО</t>
         </is>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12430,10 +14259,15 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Банк</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12461,15 +14295,972 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
           <t>Агрегатор</t>
         </is>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G66"/>
+  <autoFilter ref="A1:H66"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Домен</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>xT (0–10)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instagram.com</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Соцсети</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>yandex.ru</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Инфо</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>wikipedia.org</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Инфо</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>youtube.com</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Соцсети</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>consultant.ru</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Инфо</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>vtb.ru</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Банк (RU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>threads.com</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Соцсети</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gazprombank.ru</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Банк (RU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sberbank.ru</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Банк (RU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>raiffeisen.ru</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Банк (RU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sovcombank.ru</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Банк (RU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mtsbank.ru</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Банк (RU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>uralsib.ru</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Банк (RU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>bcc.kz</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>alfabank.ru</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Банк (RU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>halykbank.kz</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>banki.ru</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Агрегатор</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>maritimebank.com</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Банк (RU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>domrfbank.ru</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Банк (RU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kaspi.kz</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2gis.kz</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Справочник</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>krisha.kz</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Портал</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>forte.kz</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>gov.kz</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Гос</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sky.pro</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Инфо</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>userecho.ru</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Инфо</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>solva.kz</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>МФО</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>bankffin.kz</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>kmf.kz</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>МФО</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>hcsbk.kz</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>eubank.kz</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>tascredit.kz</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>МФО</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cdb.kz</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Гос</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fpa.ru</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Инфо</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>bankrbk.kz</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>berekebank.kz</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>finance.kz</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Агрегатор</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>altynbank.kz</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>nurbank.kz</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>anti-crisis.xn</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Инфо</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>home.kz</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>kzibank.kz</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>vtb-bank.kz</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>vbr.kz</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Агрегатор</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>alataucitybank.kz</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Банк</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>netdolgoff.ru</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Инфо</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>prodengi.kz</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Агрегатор</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>seiflombard.kz</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ломбард</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cashdrive.kz</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>МФО</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>avto-lombard.kz</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ломбард</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>jetcar.kz</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>МФО</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>credit-auto.kz</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ломбард</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>avto-dengi.kz</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ломбард</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>auto-money.kz</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ломбард</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>zhana-credit.kz</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>МФО</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>capitalinvest.kz</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>МФО</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>lombard-almaty.kz</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ломбард</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>lombard-b.kz</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ломбард</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>mycarfinance.kz</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>МФО</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>vsebanki.kz</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Агрегатор</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>lombard-econom.kz</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ломбард</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>